--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DE561E-29B8-4563-AD25-FB90639443A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD32F95-A613-41DA-9783-7491C41C2EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -68,55 +68,28 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
+    <t>Priscila Oliveira</t>
+  </si>
+  <si>
+    <t>AUU0D25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">953467231CR207251 </t>
+  </si>
+  <si>
+    <t>SOL7D58</t>
+  </si>
+  <si>
+    <t>9BWAG5R14ST067782</t>
+  </si>
+  <si>
+    <t>AVI0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGWFFUA59SH927276 </t>
+  </si>
+  <si>
     <t>Weldja</t>
-  </si>
-  <si>
-    <t>SDS5A37</t>
-  </si>
-  <si>
-    <t>9BM958186NB272673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHX9E38  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BM958186NB252025 </t>
-  </si>
-  <si>
-    <t>JCO3J32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWCH6CH8RP036247 </t>
-  </si>
-  <si>
-    <t>BEH9F59</t>
-  </si>
-  <si>
-    <t>8AJBA3FSXN0315894</t>
-  </si>
-  <si>
-    <t>PDB8277</t>
-  </si>
-  <si>
-    <t>8A1FC1605GL740189</t>
-  </si>
-  <si>
-    <t>QVM9G64</t>
-  </si>
-  <si>
-    <t>9BG148MK0LC437251</t>
-  </si>
-  <si>
-    <t>BZG7H44</t>
-  </si>
-  <si>
-    <t>9BHCR41BBPP402627</t>
-  </si>
-  <si>
-    <t>RUD7F00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWBH6BF9N4033347 </t>
   </si>
 </sst>
 </file>
@@ -619,13 +592,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>9</v>
@@ -634,18 +607,18 @@
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>130860046</v>
+        <v>130834374</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>9</v>
@@ -654,131 +627,46 @@
         <v>8</v>
       </c>
       <c r="F3" s="4">
-        <v>130853201</v>
+        <v>130845904</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F4" s="4">
-        <v>130887703</v>
+        <v>130846268</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>45667</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4">
-        <v>130887629</v>
-      </c>
+      <c r="A5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>45670</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4">
-        <v>130905330</v>
-      </c>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>45670</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4">
-        <v>130910143</v>
-      </c>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>45670</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4">
-        <v>130914488</v>
-      </c>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>45670</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4">
-        <v>130916471</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD32F95-A613-41DA-9783-7491C41C2EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1C8297-DEE6-4F12-857D-184801A07355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -68,28 +68,19 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
+    <t>JDH0B81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98M40EU09S4033681 </t>
+  </si>
+  <si>
     <t>Priscila Oliveira</t>
   </si>
   <si>
-    <t>AUU0D25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">953467231CR207251 </t>
-  </si>
-  <si>
-    <t>SOL7D58</t>
-  </si>
-  <si>
-    <t>9BWAG5R14ST067782</t>
-  </si>
-  <si>
-    <t>AVI0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGWFFUA59SH927276 </t>
-  </si>
-  <si>
-    <t>Weldja</t>
+    <t>QXF7D81</t>
+  </si>
+  <si>
+    <t>98861115XLK270484</t>
   </si>
 </sst>
 </file>
@@ -592,32 +583,32 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45664</v>
+        <v>45671</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4">
-        <v>130834374</v>
+        <v>130937561</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45664</v>
+        <v>45671</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -627,31 +618,16 @@
         <v>8</v>
       </c>
       <c r="F3" s="4">
-        <v>130845904</v>
+        <v>130937066</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>45664</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4">
-        <v>130846268</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3FFA57-E25E-4236-8B84-1FD1C24B447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86769C26-F09D-4C40-9EE1-DB8656C8ECFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -62,49 +62,52 @@
     <t>RETORNO</t>
   </si>
   <si>
+    <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rodrigo Belisário </t>
   </si>
   <si>
-    <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
-  </si>
-  <si>
-    <t>Paula Cinali</t>
-  </si>
-  <si>
-    <t>TCJ4A37</t>
-  </si>
-  <si>
-    <t>8ADUEFC24RG568471</t>
-  </si>
-  <si>
-    <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
-  </si>
-  <si>
-    <t>SGI1D07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWBJ6BF6R4075128 </t>
+    <t>Priscila Oliveira</t>
+  </si>
+  <si>
+    <t>SKY7H19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8AJBA3CD8P1778118 </t>
+  </si>
+  <si>
+    <t>OLE3360</t>
+  </si>
+  <si>
+    <t>9BSR6X200D3827105</t>
+  </si>
+  <si>
+    <t>GES7C55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93HFC2620MZ102663 </t>
+  </si>
+  <si>
+    <t>LQV6H59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BFZB55P5E8841217 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sem placa </t>
+  </si>
+  <si>
+    <t>LYVUZH6C6RB926331</t>
+  </si>
+  <si>
+    <t>SXI9G79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BWAH5BZ0ST636821 </t>
   </si>
   <si>
     <t>Weldja</t>
-  </si>
-  <si>
-    <t>STB7A83</t>
-  </si>
-  <si>
-    <t>9BD281AKHSYF71184</t>
-  </si>
-  <si>
-    <t>RHN4G04</t>
-  </si>
-  <si>
-    <t>9886111H6MK438037</t>
-  </si>
-  <si>
-    <t>RAX1H43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8AJDA3CD6M1820614 </t>
   </si>
 </sst>
 </file>
@@ -568,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB09B44-97DE-45D1-864A-3B74F5ECE8B4}">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="11.140625" style="4"/>
@@ -607,7 +610,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45673</v>
+        <v>45686</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>11</v>
@@ -616,97 +619,114 @@
         <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>130854709</v>
+        <v>131129206</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45673</v>
+        <v>45686</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="4">
-        <v>130965526</v>
+        <v>131134618</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>45673</v>
+        <v>45686</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4">
-        <v>130964707</v>
+        <v>131133810</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>45673</v>
+        <v>45686</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4">
-        <v>130971217</v>
+        <v>131137315</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>45673</v>
+        <v>45686</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4">
+        <v>131138549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>45686</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="4">
-        <v>130978759</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
+      <c r="D7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="4">
+        <v>131139217</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
@@ -730,14 +750,15 @@
       <c r="A14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="A16" s="3"/>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -822,7 +843,6 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
-      <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
@@ -1069,9 +1089,6 @@
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="3"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86769C26-F09D-4C40-9EE1-DB8656C8ECFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C07FE3-B556-4FAB-BF06-AD25827A7E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
+    <workbookView xWindow="345" yWindow="1215" windowWidth="23040" windowHeight="10575" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -71,43 +71,16 @@
     <t>Priscila Oliveira</t>
   </si>
   <si>
-    <t>SKY7H19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8AJBA3CD8P1778118 </t>
-  </si>
-  <si>
-    <t>OLE3360</t>
-  </si>
-  <si>
-    <t>9BSR6X200D3827105</t>
-  </si>
-  <si>
-    <t>GES7C55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93HFC2620MZ102663 </t>
-  </si>
-  <si>
-    <t>LQV6H59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BFZB55P5E8841217 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sem placa </t>
-  </si>
-  <si>
-    <t>LYVUZH6C6RB926331</t>
-  </si>
-  <si>
-    <t>SXI9G79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAH5BZ0ST636821 </t>
-  </si>
-  <si>
-    <t>Weldja</t>
+    <t>TMF6C33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BHCP51BBSP604612 </t>
+  </si>
+  <si>
+    <t>BBQ4242</t>
+  </si>
+  <si>
+    <t>9BHGC813BJP055042</t>
   </si>
 </sst>
 </file>
@@ -610,7 +583,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>11</v>
@@ -625,12 +598,12 @@
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>131129206</v>
+        <v>131150489</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
@@ -645,88 +618,22 @@
         <v>9</v>
       </c>
       <c r="F3" s="4">
-        <v>131134618</v>
+        <v>131150098</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>45686</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4">
-        <v>131133810</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>45686</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="4">
-        <v>131137315</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>45686</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4">
-        <v>131138549</v>
-      </c>
+      <c r="A6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>45686</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="4">
-        <v>131139217</v>
-      </c>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE04122-R0261031\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D69ACFC-43A3-45A3-90AB-E602982993AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33F1354-67E1-41A4-B724-16259027612A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19560" windowHeight="10035" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -61,34 +61,16 @@
     <t>RETORNO</t>
   </si>
   <si>
-    <t xml:space="preserve">Rodrigo Belisário </t>
-  </si>
-  <si>
-    <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
-  </si>
-  <si>
-    <t>QTM6J12</t>
-  </si>
-  <si>
-    <t>SADFA2BX3L1Z87726</t>
-  </si>
-  <si>
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
-    <t>QMU6B74</t>
-  </si>
-  <si>
-    <t>JKB8099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">935FCKFVYCB591226 </t>
-  </si>
-  <si>
-    <t>Jacqueline Coelho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            9UWSHX76AJN021493</t>
+    <t>SPH6B42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BRKYAAG0R0679874 </t>
+  </si>
+  <si>
+    <t>Weldja</t>
   </si>
 </sst>
 </file>
@@ -594,63 +576,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4">
-        <v>131392983</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>45706</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="4">
-        <v>131395659</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>45706</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="4">
-        <v>131398109</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE04122-R0261031\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64219B54-C811-4FF9-8E13-EAA08BB4DC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA3F3E2-26CA-4AF1-9F34-4D9D352C6CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19560" windowHeight="10035" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -64,46 +64,46 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
-    <t>Priscila Oliveira</t>
-  </si>
-  <si>
-    <t>IPP0505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8AJFZ29G066018658 </t>
-  </si>
-  <si>
     <t>Weldja</t>
   </si>
   <si>
-    <t>OKO4899</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rodrigo Belisário </t>
   </si>
   <si>
-    <t>FGV4E93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93HRV2850MK200961 </t>
-  </si>
-  <si>
-    <t>Jacqueline Coelho</t>
-  </si>
-  <si>
-    <t>TMC0E46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">988591275RKR85356 </t>
-  </si>
-  <si>
-    <t>SVC9D25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">988675AJDSKM93128 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">             9BD197134D3030104</t>
+    <t>IZS9H92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8AJBA3FS4L0278032 </t>
+  </si>
+  <si>
+    <t>POT3G62</t>
+  </si>
+  <si>
+    <t>9BSR6X400L3976656</t>
+  </si>
+  <si>
+    <t>GHI2F95</t>
+  </si>
+  <si>
+    <t>93ZC35B01K8487472</t>
+  </si>
+  <si>
+    <t>PAW3B99</t>
+  </si>
+  <si>
+    <t>9BRBD3HE5J0347087</t>
+  </si>
+  <si>
+    <t>SHU3A22</t>
+  </si>
+  <si>
+    <t>9BD281B8GPYY65934</t>
+  </si>
+  <si>
+    <t>JBR3F65</t>
+  </si>
+  <si>
+    <t>8AJKA3CD6N3104261</t>
   </si>
 </sst>
 </file>
@@ -218,7 +218,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -250,9 +250,6 @@
     </xf>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -609,47 +606,47 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4">
-        <v>131440864</v>
+        <v>131461052</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>22</v>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4">
-        <v>131449752</v>
+        <v>131461512</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
@@ -661,54 +658,71 @@
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4">
-        <v>131444898</v>
+        <v>131462226</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4">
-        <v>131456870</v>
+        <v>131463566</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>131460135</v>
+        <v>131480109</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3">
+        <v>45712</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4">
+        <v>131485044</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F629F6CF-E55A-47A7-BA5A-1594874DD3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AB5990-FE6F-4260-85C9-7A345BD8E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
+    <workbookView xWindow="690" yWindow="1560" windowWidth="23040" windowHeight="10575" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -65,79 +65,25 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
-    <t>Weldja</t>
+    <t>Carolina Lima</t>
+  </si>
+  <si>
+    <t>POU5E02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BGEY48H0LG200829 </t>
+  </si>
+  <si>
+    <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
   </si>
   <si>
     <t>Jacqueline Coelho</t>
   </si>
   <si>
-    <t xml:space="preserve">Rodrigo Belisário </t>
-  </si>
-  <si>
-    <t>JAT9C95</t>
-  </si>
-  <si>
-    <t>95PBCK51DNB021181</t>
-  </si>
-  <si>
-    <t>BWW4B09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BGEY69H0LG122959  </t>
-  </si>
-  <si>
-    <t>SJU8G30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BSR6X400R4063894  </t>
-  </si>
-  <si>
-    <t>SRZ7G29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWBJ6BF7S4020046  </t>
-  </si>
-  <si>
-    <t>QXU0D90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BHCN51AALP071251 </t>
-  </si>
-  <si>
-    <t>Paula Cinali</t>
-  </si>
-  <si>
-    <t>RHG3B28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BD358A4NNYL32347 </t>
-  </si>
-  <si>
-    <t>ASY8E84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8BCLCN6BYEG512380                    </t>
-  </si>
-  <si>
-    <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
-  </si>
-  <si>
-    <t>SWH1D28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGXCE4CC9R0018718  </t>
-  </si>
-  <si>
-    <t>RXX1F41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93ZC053CZP8505383 </t>
-  </si>
-  <si>
-    <t>FLY4576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       9BFZF55P7E8002724                     </t>
+    <t>SRN8D70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BD281BMTRYE98793 </t>
   </si>
 </sst>
 </file>
@@ -640,210 +586,75 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45737</v>
+        <v>45747</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4">
+        <v>131903623</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>45747</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="4">
-        <v>131781753</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4">
+        <v>131943198</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>45740</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4">
-        <v>131807733</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4">
-        <v>131810179</v>
-      </c>
+      <c r="A6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4">
-        <v>131810039</v>
-      </c>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="4">
-        <v>131812713</v>
-      </c>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4">
-        <v>131813773</v>
-      </c>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="4">
-        <v>131816876</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4">
-        <v>131817011</v>
-      </c>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4">
-        <v>131826497</v>
-      </c>
+      <c r="A12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>45741</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="4">
-        <v>131821116</v>
-      </c>
+      <c r="A13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao.xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D0BF31-D3E8-4964-A1D0-601925CEB9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B56E5E-3FA3-4FAD-B287-C886CD3EC3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -65,64 +65,28 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
-    <t>Jacqueline Coelho</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rodrigo Belisário </t>
   </si>
   <si>
-    <t>QCN3453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BSR6X400L3971020 </t>
-  </si>
-  <si>
     <t>Priscila Oliveira</t>
   </si>
   <si>
-    <t>FFP7D45</t>
-  </si>
-  <si>
-    <t>9BWDA05U4DT251222</t>
-  </si>
-  <si>
-    <t>GJJ1834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9UWSHX76AJN021467 </t>
-  </si>
-  <si>
-    <t>OUI4903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BFZB55P5E8852685 </t>
-  </si>
-  <si>
-    <t>Weldja</t>
-  </si>
-  <si>
-    <t>JAU3C69</t>
-  </si>
-  <si>
-    <t>9BD341ACXNY750507</t>
-  </si>
-  <si>
-    <t>JCS4I44</t>
-  </si>
-  <si>
-    <t>1FTFW1E50PFC17171</t>
-  </si>
-  <si>
-    <t>OHO8J32</t>
-  </si>
-  <si>
-    <t>8AJFA8CB5L2008847</t>
-  </si>
-  <si>
-    <t>RAP6E29</t>
-  </si>
-  <si>
-    <t>93HFC2660LZ122032</t>
+    <t>CUL7F77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BVRG40D8ME886146 </t>
+  </si>
+  <si>
+    <t>SDW5D13</t>
+  </si>
+  <si>
+    <t>9BD281B9JPYX86798</t>
+  </si>
+  <si>
+    <t>BVZ9I76</t>
+  </si>
+  <si>
+    <t>8AJBA3FSXN0306094</t>
   </si>
 </sst>
 </file>
@@ -625,7 +589,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>11</v>
@@ -637,41 +601,41 @@
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>132142040</v>
+        <v>132166526</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4">
-        <v>132143592</v>
+        <v>132168993</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>8</v>
@@ -680,108 +644,24 @@
         <v>9</v>
       </c>
       <c r="F4" s="4">
-        <v>132157048</v>
+        <v>132182741</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>45762</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4">
-        <v>132156649</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>45762</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4">
-        <v>132148106</v>
-      </c>
+      <c r="A6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>45762</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="4">
-        <v>132151724</v>
-      </c>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>45762</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4">
-        <v>132164012</v>
-      </c>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>45762</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4">
-        <v>132123737</v>
-      </c>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
